--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N107_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N107_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.56898258843881</v>
+        <v>11.95495967062131</v>
       </c>
       <c r="D2" t="n">
-        <v>46.02669675048803</v>
+        <v>7.479338221954305</v>
       </c>
       <c r="E2" t="n">
-        <v>5.730670668031304</v>
+        <v>0.931233983555087</v>
       </c>
       <c r="F2" t="n">
-        <v>17.55688668858251</v>
+        <v>2.852994086894657</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.20185899558528</v>
+        <v>10.10780208678261</v>
       </c>
       <c r="D3" t="n">
-        <v>23.57493501803356</v>
+        <v>3.830926940430454</v>
       </c>
       <c r="E3" t="n">
-        <v>5.730670668031304</v>
+        <v>0.931233983555087</v>
       </c>
       <c r="F3" t="n">
-        <v>17.55688668858251</v>
+        <v>2.852994086894657</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.67336878550208</v>
+        <v>9.696922427644088</v>
       </c>
       <c r="D4" t="n">
-        <v>59.22352816404882</v>
+        <v>9.623823326657934</v>
       </c>
       <c r="E4" t="n">
-        <v>5.730670668031304</v>
+        <v>0.931233983555087</v>
       </c>
       <c r="F4" t="n">
-        <v>17.55688668858251</v>
+        <v>2.852994086894657</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>70.53918178702243</v>
+        <v>11.46261704039114</v>
       </c>
       <c r="D5" t="n">
-        <v>70.82936028891693</v>
+        <v>11.509771046949</v>
       </c>
       <c r="E5" t="n">
-        <v>5.730670668031304</v>
+        <v>0.931233983555087</v>
       </c>
       <c r="F5" t="n">
-        <v>17.55688668858251</v>
+        <v>2.852994086894657</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
